--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Inquisition_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Inquisition_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R344e879e7b694ab0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R4d2c45cae632489c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rcd175bbfa2034835"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R84d5f0d495e841ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rf52aa73bc7904edb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R6b98a947d9ff406f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R5fe0413460334fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1df88f8a2cf94937"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R3844701ad3fe446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R71da7b2ed85e40b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R565e4f0a1015457d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rf4c23ed51b96467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R36255c689f3e4f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R1ef945aef4984032"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R890b445498a4481b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R1fd254b4ef0a426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R1badb0984f134321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R96261c04da9f403c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R0b737223c2bc44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4e1f0c1bd82f4310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rfba24a961b6e4c1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rc21925fc302c4185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R163c5bc377484dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rce68a3726df74aaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Ra2a761cada654c58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfd155f2b9cb54938"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rfb3c2d1650544deb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Re45878ac780943a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1f08f0ba6f394195"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rdbcdc73f74c54004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rcd391d94f7744a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R552be07a08e341a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rff4a723990414964"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R9b2e36dc8ff845df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R6c6e50a9d2f245cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1e26403707494e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R8169cacee2a447a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rfe7db9e112164054"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R892b2d7ca87942df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R3f93a2574b414745"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R64e8bf1494f143ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Red9fad2e561c4642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R002c548d24344a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9d4aa95d9886497e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Re17a42f7d5444405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7720c63d1d234840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rf90df1062b7f457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R8e18b013efd140e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra3c84875b162463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R06d815061edf4706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc6933bcc81804db4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rb49bc11675344f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4a04fea050634392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf3c1c85d579543e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R8c727c562766482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2cc41fa4ff694eb7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>63</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>9</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>51</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Défini")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$12,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
+        <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
-        <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$9,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$12,"P0")</x:f>
         <x:v>6</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4048,10 +4042,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4087,7 +4081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58b75611b4ce4c0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R205146bcb0cb449c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4227,61 +4221,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4335,8 +4329,8 @@
         <x:v>Conception originale rattachée à Mass Effect: Inquisition, récit court</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4388,8 +4382,8 @@
         <x:v>Conception originale rattachée à Mass Effect: Inquisition, récit court</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4441,8 +4435,8 @@
         <x:v>Conception originale rattachée à Mass Effect: Inquisition, récit court</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -4476,7 +4470,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84c718316d9d402a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e028c206b1d44c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4616,61 +4610,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4724,8 +4718,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4777,8 +4771,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4830,8 +4824,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -4865,7 +4859,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e2ccf42be0401e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa9111e71d3d41c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5005,61 +4999,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5113,8 +5107,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5166,8 +5160,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5219,8 +5213,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5254,7 +5248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23931fa215264645"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb48a4eba5eb6412d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5394,61 +5388,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5502,8 +5496,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5555,8 +5549,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5608,8 +5602,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5643,7 +5637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f41dd91e7044676"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64ccaba557df46e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5783,61 +5777,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5889,8 +5883,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5940,8 +5934,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5991,8 +5985,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -6026,7 +6020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92a5f355c2c04642"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb489d924a55f446b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6166,61 +6160,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6272,8 +6266,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -6307,7 +6301,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b7164a78c84440f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R481ba05b385b44e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6447,61 +6441,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6553,8 +6547,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -6588,7 +6582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8016233eb804407"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R598bb1fb83684b1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6728,61 +6722,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6834,8 +6828,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -6869,7 +6863,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c2dd45cc3814665"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R300ca1cd91934799"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7009,61 +7003,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7117,8 +7111,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7152,7 +7146,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0743381ff004322"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619d7ee2640b497c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7292,61 +7286,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7400,10 +7394,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INQ-S-PAIR</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://books.apple.com/gr/book/mass-effect-incursion-inquisition/id1047054838</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -7457,10 +7451,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -7496,7 +7490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raed9f6aa16814112"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R831aa6e6d04f42c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7636,61 +7630,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7744,8 +7738,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7797,8 +7791,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -7832,7 +7826,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5f1f20a7a76467a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcf66e07a198427b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7972,61 +7966,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8078,8 +8072,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8129,8 +8123,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8180,8 +8174,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8231,8 +8225,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -8266,7 +8260,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf14ee7bdd7c4a15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d9cfa2359645c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8406,61 +8400,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8510,8 +8504,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8559,8 +8553,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8608,8 +8602,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8657,8 +8651,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -8692,7 +8686,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ee3026b62b34029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a3d456b99294663"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8832,61 +8826,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8938,8 +8932,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8989,8 +8983,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9040,8 +9034,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -9075,7 +9069,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc967cea32884e14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82a5cd7887c744d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9215,61 +9209,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9323,8 +9317,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -9358,7 +9352,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0958f001d8243a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a822dfaab0d4f16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9498,61 +9492,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9600,8 +9594,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9647,8 +9641,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9694,8 +9688,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9741,8 +9735,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9776,7 +9770,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44ae658d8a704c8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e1e7aec4ca74b4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9916,61 +9910,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10018,8 +10012,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10065,8 +10059,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10112,8 +10106,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10157,8 +10151,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10202,8 +10196,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10247,8 +10241,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -10282,7 +10276,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad201c51a3e3484f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R254f66a6aab64f40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10422,61 +10416,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10522,8 +10516,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10567,8 +10561,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -10602,7 +10596,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e31ba5d0e5c437a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a551f96590c4418"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10667,10 +10661,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -10719,7 +10713,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Adaptation d’enquête compacte avec sources d’information attribuées, confrontation courte et rapport. Les branches proposées changent la méthode, pas le verdict canon.</x:v>
+        <x:v>63 fiches de production ; 2 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -10738,11 +10732,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -10895,22 +10889,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -10979,13 +10973,13 @@
       <x:c r="F31" s="2"/>
     </x:row>
     <x:row r="32" ht="34" customHeight="1">
-      <x:c r="A32" s="30" t="str">
+      <x:c r="A32" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B32" s="31" t="str">
+      <x:c r="B32" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C32" s="32" t="str">
+      <x:c r="C32" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D32" s="2"/>
@@ -11356,10 +11350,16 @@
       <x:c r="E58" s="2"/>
       <x:c r="F58" s="2"/>
     </x:row>
-    <x:row r="59" ht="22" customHeight="1">
-      <x:c r="A59" s="2"/>
-      <x:c r="B59" s="2"/>
-      <x:c r="C59" s="2"/>
+    <x:row r="59" ht="96" customHeight="1">
+      <x:c r="A59" s="6" t="str">
+        <x:v>Complément lectures contextualisées</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
+        <x:v>2 références supplémentaires au stade Prototype dans 1 parcours de lecture (1 pages de paraphrases documentaires sourcées), limités à leurs segments exacts.</x:v>
+      </x:c>
+      <x:c r="C59" s="6" t="str">
+        <x:v>Les faits, références, sources et réserves d’origine sont conservés. Ces lectures ne constituent ni un découpage intégral, ni une scène jouable, ni un recrutement ; modèles, voix et animations de l’œuvre ne sont pas produits.</x:v>
+      </x:c>
       <x:c r="D59" s="2"/>
       <x:c r="E59" s="2"/>
       <x:c r="F59" s="2"/>
@@ -11915,6 +11915,14 @@
       <x:c r="D128" s="2"/>
       <x:c r="E128" s="2"/>
       <x:c r="F128" s="2"/>
+    </x:row>
+    <x:row r="129" ht="22" customHeight="1">
+      <x:c r="A129" s="2"/>
+      <x:c r="B129" s="2"/>
+      <x:c r="C129" s="2"/>
+      <x:c r="D129" s="2"/>
+      <x:c r="E129" s="2"/>
+      <x:c r="F129" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12056,61 +12064,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12164,10 +12172,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -12221,10 +12229,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -12260,7 +12268,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3740e91eb8f45f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree57593742d54824"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12287,7 +12295,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="71" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -12400,65 +12408,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>INQ-REF-SCOPE</x:v>
       </x:c>
@@ -12466,7 +12474,7 @@
         <x:v>Bailey au centre de l’enquête</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -12485,7 +12493,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Livrable proposé : spécification INQ/lore/ref-scope; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire INQ-REF-SCOPE consultable dans les lectures inq-bailey de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Vérifier toute précision non contenue dans cette notice avant de la déclarer canon.</x:v>
@@ -12500,11 +12508,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INQ-S-PAIR</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://books.apple.com/gr/book/mass-effect-incursion-inquisition/id1047054838</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les soupçons d’Inquisition restent attribués à leur notice, sans verdict inventé. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
@@ -12549,10 +12557,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -12598,10 +12606,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -12647,10 +12655,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -12696,10 +12704,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -12745,10 +12753,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>INQ-S-WIKI</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Inquisition</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -12784,7 +12792,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R503bf1c765634923"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0139ba6f2ce34f96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12811,7 +12819,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="71" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="90" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -12924,65 +12932,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>INQ-WRL-CITADEL</x:v>
       </x:c>
@@ -12990,7 +12998,7 @@
         <x:v>Citadelle — enquête de Bailey</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -13011,7 +13019,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Livrable proposé : spécification INQ/worlds/wrl-citadel; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire INQ-WRL-CITADEL consultable dans les lectures inq-bailey de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Conserver la confrontation publiée et l’incertitude finale; une option de dialogue n’établit pas une innocence ou une culpabilité omnisciente.</x:v>
@@ -13026,11 +13034,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INQ-S-PAIR</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://books.apple.com/gr/book/mass-effect-incursion-inquisition/id1047054838</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les soupçons d’Inquisition restent attribués à leur notice, sans verdict inventé. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13065,7 +13073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b34c522f6c047cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bb6c54ffd434348"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13205,61 +13213,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13311,8 +13319,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -13346,7 +13354,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1605a8e3d0745d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32d882a4ae0a44c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13486,61 +13494,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13590,8 +13598,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -13625,7 +13633,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01f21836216d4840"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa4255b3e2be4e83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13765,61 +13773,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13869,8 +13877,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -13904,7 +13912,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2130b32bf1f944ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc67c17525b95422f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14044,61 +14052,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14152,8 +14160,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14205,8 +14213,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -14258,8 +14266,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -14293,7 +14301,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R718ea8d97dd34912"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b0f27992174794"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Inquisition_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Inquisition_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1f08f0ba6f394195"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rdbcdc73f74c54004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rcd391d94f7744a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R552be07a08e341a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rff4a723990414964"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R9b2e36dc8ff845df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R6c6e50a9d2f245cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1e26403707494e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R8169cacee2a447a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rfe7db9e112164054"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R892b2d7ca87942df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R3f93a2574b414745"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R64e8bf1494f143ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Red9fad2e561c4642"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R002c548d24344a3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9d4aa95d9886497e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Re17a42f7d5444405"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R7720c63d1d234840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rf90df1062b7f457c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R8e18b013efd140e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra3c84875b162463c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R06d815061edf4706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc6933bcc81804db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rb49bc11675344f96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4a04fea050634392"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf3c1c85d579543e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R8c727c562766482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2cc41fa4ff694eb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6acc96d94eb34aea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R8e180a04257941e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Re2af8946c3954650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R1c58230f358b41df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rffb8364043ea40af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R23155dbcdbd74807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4751f6a9e8884178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re4d8b40561544825"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra790a140b8754c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Re6f51312fd5f4fc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Re0986286279645cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7e0cc95db0ee4a6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rc28b223423df4fb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R34e4f551cd2f4d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R54e5e663568d4e61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rb4062dee892e4c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R552d13613be74795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Ra23e12be7a894be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Re80646825d824d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Ree1f2eeb2bd94357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Re261c794b72d4921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R99f444c8a5fe4665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfc18ec40402a4740"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbeb91d2a28234d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R22ffda37ca5c466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Recf6da55f91b4407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R86467f9f926c4090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1389c07f98c841fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4081,7 +4081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R205146bcb0cb449c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31a996e34ae841da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4470,7 +4470,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e028c206b1d44c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba9277e2e0f847ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4859,7 +4859,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa9111e71d3d41c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree653f7b245c4c39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5248,7 +5248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb48a4eba5eb6412d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1155d9af1083439b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5637,7 +5637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64ccaba557df46e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06624d7fc99e4cd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6020,7 +6020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb489d924a55f446b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67570addab8d4ff3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6301,7 +6301,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R481ba05b385b44e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c74fe6e93c74039"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6582,7 +6582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R598bb1fb83684b1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb65bcf1ec5ce432b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6863,7 +6863,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R300ca1cd91934799"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc19946105f96499b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7146,7 +7146,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619d7ee2640b497c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e50d6fe9916417c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7490,7 +7490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R831aa6e6d04f42c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53f7c377298c4e33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7826,7 +7826,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcf66e07a198427b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ce4e4d7e81441a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8260,7 +8260,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d9cfa2359645c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62410c7675e44eb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8686,7 +8686,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a3d456b99294663"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87354426bd794bfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9069,7 +9069,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82a5cd7887c744d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda75a0a98fa54bad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9352,7 +9352,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a822dfaab0d4f16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf6834cff67c42ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9770,7 +9770,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e1e7aec4ca74b4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1fa63497a14ef7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10276,7 +10276,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R254f66a6aab64f40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f36654abd4d4c79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10596,7 +10596,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a551f96590c4418"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c75b83bea7c4dc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12268,7 +12268,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree57593742d54824"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74710d0a38e349ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12792,7 +12792,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0139ba6f2ce34f96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02aa5ed7874547a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13073,7 +13073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bb6c54ffd434348"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de3587a41034153"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13354,7 +13354,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32d882a4ae0a44c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e084ae6a1fc465f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13633,7 +13633,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa4255b3e2be4e83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra624c2bfa6cb45a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13912,7 +13912,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc67c17525b95422f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e2781a5539448b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14301,7 +14301,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b0f27992174794"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09c5f360f85244a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Inquisition_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Inquisition_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6acc96d94eb34aea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R8e180a04257941e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Re2af8946c3954650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R1c58230f358b41df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rffb8364043ea40af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R23155dbcdbd74807"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4751f6a9e8884178"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re4d8b40561544825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra790a140b8754c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Re6f51312fd5f4fc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Re0986286279645cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7e0cc95db0ee4a6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rc28b223423df4fb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R34e4f551cd2f4d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R54e5e663568d4e61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rb4062dee892e4c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R552d13613be74795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Ra23e12be7a894be3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Re80646825d824d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Ree1f2eeb2bd94357"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Re261c794b72d4921"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R99f444c8a5fe4665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfc18ec40402a4740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rbeb91d2a28234d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R22ffda37ca5c466b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Recf6da55f91b4407"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R86467f9f926c4090"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1389c07f98c841fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R36044f486d564365"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Re64364d7c1934757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R89ea3b403174413b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R2219ce82828841fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Ra87ba17902d346ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R580539bc76034379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rcee268be7ba34451"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc7b6d59e66c24791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rf66eda51172d4c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rb71f33970c174bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rcd0a196dd2cf494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R2dbf1b2a42b84254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R655fe7289ea24690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R4fbcde2611a240f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rf7ffdd1f155e4437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R41317e56ad6e4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R587461c49c074485"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R16f3dfdbe8a146c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rfb424684e3e44e6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R3c403f0c8b4d4335"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra464bcf668b841de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R11f7794640684edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R806963dadd6c4f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rffab14eb199f4e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4a2fc4991ab64fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R2b4d526485594c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rca629ac055e44859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R039c4a920a9b4137"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4081,7 +4081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31a996e34ae841da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1134369a99104da0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4470,7 +4470,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba9277e2e0f847ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95636c86eb8848f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4859,7 +4859,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree653f7b245c4c39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09edc8dc0d294f83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5248,7 +5248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1155d9af1083439b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa4bcb1362144464"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5637,7 +5637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06624d7fc99e4cd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf98580b01686463f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6020,7 +6020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67570addab8d4ff3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd554e58aaf3e4001"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6301,7 +6301,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c74fe6e93c74039"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R081a1df1e7e44f0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6582,7 +6582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb65bcf1ec5ce432b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07f9ce784d774199"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6863,7 +6863,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc19946105f96499b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb96232f787b4a37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7146,7 +7146,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e50d6fe9916417c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac806a1a1bf4436"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7490,7 +7490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53f7c377298c4e33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9bf72b5cd1b40f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7826,7 +7826,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ce4e4d7e81441a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2a326ef35e045a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8260,7 +8260,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62410c7675e44eb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca8aee42ab0a4ae6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8686,7 +8686,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87354426bd794bfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf1f903ed23344ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9069,7 +9069,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda75a0a98fa54bad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97071a1a2038484b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9352,7 +9352,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf6834cff67c42ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde4a614129dc4d23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9770,7 +9770,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1fa63497a14ef7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96fbe8f3638f41a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10276,7 +10276,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f36654abd4d4c79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86de20cd9b5d497e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10596,7 +10596,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c75b83bea7c4dc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99548987fb594181"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12268,7 +12268,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74710d0a38e349ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c3fc47dfa724f71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12792,7 +12792,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02aa5ed7874547a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2da64a7a5bf64886"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13073,7 +13073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de3587a41034153"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R463de148a7d04f01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13354,7 +13354,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e084ae6a1fc465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0e069d90624aed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13633,7 +13633,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra624c2bfa6cb45a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77de13929a74fe5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13912,7 +13912,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e2781a5539448b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03ba96b73ba04555"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14301,7 +14301,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09c5f360f85244a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb69150dd0d244f50"/>
   </x:tableParts>
 </x:worksheet>
 </file>